--- a/result/Table202601.xlsx
+++ b/result/Table202601.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -663,19 +663,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I5" t="n">
         <v>17.35</v>
       </c>
       <c r="J5" t="n">
-        <v>13.79</v>
+        <v>12.47</v>
       </c>
       <c r="K5" t="n">
-        <v>-20.52</v>
+        <v>-28.13</v>
       </c>
       <c r="L5" t="n">
-        <v>-20518.73</v>
+        <v>-28126.8</v>
       </c>
     </row>
     <row r="6">
@@ -750,7 +750,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -759,19 +759,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I7" t="n">
         <v>27.27</v>
       </c>
       <c r="J7" t="n">
-        <v>15.9</v>
+        <v>15.22</v>
       </c>
       <c r="K7" t="n">
-        <v>-41.69</v>
+        <v>-44.19</v>
       </c>
       <c r="L7" t="n">
-        <v>-41694.17</v>
+        <v>-44187.75</v>
       </c>
     </row>
     <row r="8">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I13" t="n">
         <v>4.34</v>
       </c>
       <c r="J13" t="n">
-        <v>3.41</v>
+        <v>3.23</v>
       </c>
       <c r="K13" t="n">
-        <v>-21.43</v>
+        <v>-25.58</v>
       </c>
       <c r="L13" t="n">
-        <v>-21428.57</v>
+        <v>-25576.04</v>
       </c>
     </row>
     <row r="14">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1347,19 +1347,19 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I19" t="n">
         <v>5.18</v>
       </c>
       <c r="J19" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="K19" t="n">
-        <v>-44.4</v>
+        <v>-44.79</v>
       </c>
       <c r="L19" t="n">
-        <v>-44401.54</v>
+        <v>-44787.64</v>
       </c>
     </row>
     <row r="20">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1447,19 +1447,19 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I21" t="n">
         <v>15.63</v>
       </c>
       <c r="J21" t="n">
-        <v>11.31</v>
+        <v>10.89</v>
       </c>
       <c r="K21" t="n">
-        <v>-27.64</v>
+        <v>-30.33</v>
       </c>
       <c r="L21" t="n">
-        <v>-27639.16</v>
+        <v>-30326.3</v>
       </c>
     </row>
     <row r="22">

--- a/result/Table202601.xlsx
+++ b/result/Table202601.xlsx
@@ -516,24 +516,24 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="I2" t="n">
         <v>11.82</v>
       </c>
       <c r="J2" t="n">
-        <v>12.09</v>
+        <v>13.52</v>
       </c>
       <c r="K2" t="n">
-        <v>2.28</v>
+        <v>14.38</v>
       </c>
       <c r="L2" t="n">
-        <v>2284.26</v>
+        <v>14382.4</v>
       </c>
     </row>
     <row r="3">
@@ -562,24 +562,24 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
         <v>7.92</v>
       </c>
       <c r="J3" t="n">
-        <v>7.42</v>
+        <v>6.82</v>
       </c>
       <c r="K3" t="n">
-        <v>-6.31</v>
+        <v>-13.89</v>
       </c>
       <c r="L3" t="n">
-        <v>-6313.13</v>
+        <v>-13888.89</v>
       </c>
     </row>
     <row r="4">
@@ -608,24 +608,24 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
         <v>3.23</v>
       </c>
       <c r="J4" t="n">
-        <v>3.07</v>
+        <v>2.89</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.95</v>
+        <v>-10.53</v>
       </c>
       <c r="L4" t="n">
-        <v>-4953.56</v>
+        <v>-10526.32</v>
       </c>
     </row>
     <row r="5">
@@ -704,24 +704,24 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
         <v>8.08</v>
       </c>
       <c r="J6" t="n">
-        <v>8.220000000000001</v>
+        <v>7.92</v>
       </c>
       <c r="K6" t="n">
-        <v>1.73</v>
+        <v>-1.98</v>
       </c>
       <c r="L6" t="n">
-        <v>1732.67</v>
+        <v>-1980.2</v>
       </c>
     </row>
     <row r="7">
@@ -850,24 +850,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
         <v>7.84</v>
       </c>
       <c r="J9" t="n">
-        <v>7.32</v>
+        <v>6.73</v>
       </c>
       <c r="K9" t="n">
-        <v>-6.63</v>
+        <v>-14.16</v>
       </c>
       <c r="L9" t="n">
-        <v>-6632.65</v>
+        <v>-14158.16</v>
       </c>
     </row>
     <row r="10">
@@ -1292,24 +1292,24 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I18" t="n">
         <v>6.15</v>
       </c>
       <c r="J18" t="n">
-        <v>5.73</v>
+        <v>5.12</v>
       </c>
       <c r="K18" t="n">
-        <v>-6.83</v>
+        <v>-16.75</v>
       </c>
       <c r="L18" t="n">
-        <v>-6829.27</v>
+        <v>-16747.97</v>
       </c>
     </row>
     <row r="19">
@@ -1534,24 +1534,24 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I23" t="n">
         <v>19.37</v>
       </c>
       <c r="J23" t="n">
-        <v>19.66</v>
+        <v>18.15</v>
       </c>
       <c r="K23" t="n">
-        <v>1.5</v>
+        <v>-6.3</v>
       </c>
       <c r="L23" t="n">
-        <v>1497.16</v>
+        <v>-6298.4</v>
       </c>
     </row>
     <row r="24">
@@ -1818,24 +1818,24 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I29" t="n">
         <v>16.06</v>
       </c>
       <c r="J29" t="n">
-        <v>15.25</v>
+        <v>16.28</v>
       </c>
       <c r="K29" t="n">
-        <v>-5.04</v>
+        <v>1.37</v>
       </c>
       <c r="L29" t="n">
-        <v>-5043.59</v>
+        <v>1369.86</v>
       </c>
     </row>
     <row r="30">
@@ -2110,24 +2110,24 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I35" t="n">
         <v>28.65</v>
       </c>
       <c r="J35" t="n">
-        <v>25.88</v>
+        <v>25.7</v>
       </c>
       <c r="K35" t="n">
-        <v>-9.67</v>
+        <v>-10.3</v>
       </c>
       <c r="L35" t="n">
-        <v>-9668.41</v>
+        <v>-10296.68</v>
       </c>
     </row>
     <row r="36">
@@ -2202,24 +2202,24 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I37" t="n">
         <v>18.88</v>
       </c>
       <c r="J37" t="n">
-        <v>17.73</v>
+        <v>15.98</v>
       </c>
       <c r="K37" t="n">
-        <v>-6.09</v>
+        <v>-15.36</v>
       </c>
       <c r="L37" t="n">
-        <v>-6091.1</v>
+        <v>-15360.17</v>
       </c>
     </row>
     <row r="38">
@@ -2440,24 +2440,24 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I42" t="n">
         <v>15.61</v>
       </c>
       <c r="J42" t="n">
-        <v>14.64</v>
+        <v>14</v>
       </c>
       <c r="K42" t="n">
-        <v>-6.21</v>
+        <v>-10.31</v>
       </c>
       <c r="L42" t="n">
-        <v>-6213.97</v>
+        <v>-10313.9</v>
       </c>
     </row>
     <row r="43">

--- a/result/Table202601.xlsx
+++ b/result/Table202601.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -663,19 +663,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I5" t="n">
         <v>17.35</v>
       </c>
       <c r="J5" t="n">
-        <v>12.47</v>
+        <v>11.22</v>
       </c>
       <c r="K5" t="n">
-        <v>-28.13</v>
+        <v>-35.33</v>
       </c>
       <c r="L5" t="n">
-        <v>-28126.8</v>
+        <v>-35331.41</v>
       </c>
     </row>
     <row r="6">
@@ -750,7 +750,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -759,19 +759,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I7" t="n">
         <v>27.27</v>
       </c>
       <c r="J7" t="n">
-        <v>15.22</v>
+        <v>15.04</v>
       </c>
       <c r="K7" t="n">
-        <v>-44.19</v>
+        <v>-44.85</v>
       </c>
       <c r="L7" t="n">
-        <v>-44187.75</v>
+        <v>-44847.82</v>
       </c>
     </row>
     <row r="8">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I13" t="n">
         <v>4.34</v>
       </c>
       <c r="J13" t="n">
-        <v>3.23</v>
+        <v>3.27</v>
       </c>
       <c r="K13" t="n">
-        <v>-25.58</v>
+        <v>-24.65</v>
       </c>
       <c r="L13" t="n">
-        <v>-25576.04</v>
+        <v>-24654.38</v>
       </c>
     </row>
     <row r="14">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1347,19 +1347,19 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I19" t="n">
         <v>5.18</v>
       </c>
       <c r="J19" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="K19" t="n">
-        <v>-44.79</v>
+        <v>-46.72</v>
       </c>
       <c r="L19" t="n">
-        <v>-44787.64</v>
+        <v>-46718.15</v>
       </c>
     </row>
     <row r="20">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1447,19 +1447,19 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I21" t="n">
         <v>15.63</v>
       </c>
       <c r="J21" t="n">
-        <v>10.89</v>
+        <v>10.71</v>
       </c>
       <c r="K21" t="n">
-        <v>-30.33</v>
+        <v>-31.48</v>
       </c>
       <c r="L21" t="n">
-        <v>-30326.3</v>
+        <v>-31477.93</v>
       </c>
     </row>
     <row r="22">

--- a/result/Table202601.xlsx
+++ b/result/Table202601.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -663,19 +663,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I5" t="n">
         <v>17.35</v>
       </c>
       <c r="J5" t="n">
-        <v>11.22</v>
+        <v>10.82</v>
       </c>
       <c r="K5" t="n">
-        <v>-35.33</v>
+        <v>-37.64</v>
       </c>
       <c r="L5" t="n">
-        <v>-35331.41</v>
+        <v>-37636.89</v>
       </c>
     </row>
     <row r="6">
@@ -750,7 +750,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -759,19 +759,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I7" t="n">
         <v>27.27</v>
       </c>
       <c r="J7" t="n">
-        <v>15.04</v>
+        <v>14.16</v>
       </c>
       <c r="K7" t="n">
-        <v>-44.85</v>
+        <v>-48.07</v>
       </c>
       <c r="L7" t="n">
-        <v>-44847.82</v>
+        <v>-48074.81</v>
       </c>
     </row>
     <row r="8">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I13" t="n">
         <v>4.34</v>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1347,19 +1347,19 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I19" t="n">
         <v>5.18</v>
       </c>
       <c r="J19" t="n">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="K19" t="n">
-        <v>-46.72</v>
+        <v>-49.42</v>
       </c>
       <c r="L19" t="n">
-        <v>-46718.15</v>
+        <v>-49420.85</v>
       </c>
     </row>
     <row r="20">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1447,19 +1447,19 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I21" t="n">
         <v>15.63</v>
       </c>
       <c r="J21" t="n">
-        <v>10.71</v>
+        <v>12</v>
       </c>
       <c r="K21" t="n">
-        <v>-31.48</v>
+        <v>-23.22</v>
       </c>
       <c r="L21" t="n">
-        <v>-31477.93</v>
+        <v>-23224.57</v>
       </c>
     </row>
     <row r="22">

--- a/result/Table202601.xlsx
+++ b/result/Table202601.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -663,19 +663,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I5" t="n">
         <v>17.35</v>
       </c>
       <c r="J5" t="n">
-        <v>10.82</v>
+        <v>10.84</v>
       </c>
       <c r="K5" t="n">
-        <v>-37.64</v>
+        <v>-37.52</v>
       </c>
       <c r="L5" t="n">
-        <v>-37636.89</v>
+        <v>-37521.61</v>
       </c>
     </row>
     <row r="6">
@@ -750,7 +750,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -759,19 +759,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I7" t="n">
         <v>27.27</v>
       </c>
       <c r="J7" t="n">
-        <v>14.16</v>
+        <v>14.05</v>
       </c>
       <c r="K7" t="n">
-        <v>-48.07</v>
+        <v>-48.48</v>
       </c>
       <c r="L7" t="n">
-        <v>-48074.81</v>
+        <v>-48478.18</v>
       </c>
     </row>
     <row r="8">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I13" t="n">
         <v>4.34</v>
       </c>
       <c r="J13" t="n">
-        <v>3.27</v>
+        <v>3.31</v>
       </c>
       <c r="K13" t="n">
-        <v>-24.65</v>
+        <v>-23.73</v>
       </c>
       <c r="L13" t="n">
-        <v>-24654.38</v>
+        <v>-23732.72</v>
       </c>
     </row>
     <row r="14">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1347,19 +1347,19 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="I19" t="n">
         <v>5.18</v>
       </c>
       <c r="J19" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="K19" t="n">
-        <v>-49.42</v>
+        <v>-49.23</v>
       </c>
       <c r="L19" t="n">
-        <v>-49420.85</v>
+        <v>-49227.8</v>
       </c>
     </row>
     <row r="20">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1447,19 +1447,19 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="I21" t="n">
         <v>15.63</v>
       </c>
       <c r="J21" t="n">
-        <v>12</v>
+        <v>11.44</v>
       </c>
       <c r="K21" t="n">
-        <v>-23.22</v>
+        <v>-26.81</v>
       </c>
       <c r="L21" t="n">
-        <v>-23224.57</v>
+        <v>-26807.42</v>
       </c>
     </row>
     <row r="22">
